--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/3022-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/3022-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF325C7C-8423-4473-8D42-AC33DF003D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E3AA55B-FE66-4B3B-BFFD-97B269EF62ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{5EF962BE-7073-4423-B57C-E8348785176E}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{DF868958-CEAE-4DBD-9518-B9D1AF273609}"/>
   </bookViews>
   <sheets>
     <sheet name="3022-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1285,21 +1285,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412CA21D-975E-4DB3-B3FD-6CAEAF4F0252}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F50D9BE-9F9B-42EB-8E6F-F16D462F2762}">
   <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="9.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" customWidth="1"/>
-    <col min="7" max="17" width="9.6640625" customWidth="1"/>
-    <col min="18" max="18" width="10.109375" customWidth="1"/>
-    <col min="19" max="20" width="9.6640625" customWidth="1"/>
-    <col min="21" max="21" width="11.77734375" customWidth="1"/>
+    <col min="1" max="3" width="7.08984375" customWidth="1"/>
+    <col min="4" max="4" width="7.453125" customWidth="1"/>
+    <col min="5" max="5" width="7.08984375" customWidth="1"/>
+    <col min="6" max="6" width="7.453125" customWidth="1"/>
+    <col min="7" max="16" width="7.08984375" customWidth="1"/>
+    <col min="17" max="17" width="7" customWidth="1"/>
+    <col min="18" max="18" width="7.36328125" customWidth="1"/>
+    <col min="19" max="20" width="7.08984375" customWidth="1"/>
+    <col min="21" max="21" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1342,7 +1343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="16"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1405,7 +1406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="17"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1452,7 +1453,7 @@
       </c>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1517,7 +1518,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2024</v>
       </c>
@@ -1582,7 +1583,7 @@
         <v>62.54</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1647,7 +1648,7 @@
         <v>57.14</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1712,7 +1713,7 @@
         <v>52.28</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1777,7 +1778,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1907,7 +1908,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
@@ -1972,7 +1973,7 @@
         <v>26.71</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2017</v>
       </c>
@@ -2037,7 +2038,7 @@
         <v>23.44</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2016</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>24.12</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2015</v>
       </c>
@@ -2167,7 +2168,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2014</v>
       </c>
@@ -2232,7 +2233,7 @@
         <v>22.03</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2013</v>
       </c>
@@ -2297,7 +2298,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2012</v>
       </c>
@@ -2362,7 +2363,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2011</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>26.34</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2010</v>
       </c>
@@ -2492,7 +2493,7 @@
         <v>22.47</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2009</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2008</v>
       </c>
@@ -2622,7 +2623,7 @@
         <v>17.91</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2007</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2006</v>
       </c>
@@ -2752,7 +2753,7 @@
         <v>18.440000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2005</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>17.16</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="10">
         <v>2004</v>
       </c>
@@ -2882,7 +2883,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2003</v>
       </c>
@@ -2947,7 +2948,7 @@
         <v>15.83</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="10">
         <v>2002</v>
       </c>
@@ -3012,7 +3013,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2001</v>
       </c>
@@ -3077,7 +3078,7 @@
         <v>17.39</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="10">
         <v>2000</v>
       </c>
@@ -3142,7 +3143,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1999</v>
       </c>
@@ -3207,7 +3208,7 @@
         <v>21.19</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="10">
         <v>1998</v>
       </c>
